--- a/excel/sign.xlsx
+++ b/excel/sign.xlsx
@@ -94,7 +94,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
   <si>
     <t>编号</t>
   </si>
@@ -136,6 +136,24 @@
   </si>
   <si>
     <t>[300001,1]</t>
+  </si>
+  <si>
+    <t>[200001,4000]</t>
+  </si>
+  <si>
+    <t>[200002,4000]</t>
+  </si>
+  <si>
+    <t>[200001,5000]</t>
+  </si>
+  <si>
+    <t>[200002,5000]</t>
+  </si>
+  <si>
+    <t>[200001,6000]</t>
+  </si>
+  <si>
+    <t>[200002,6000]</t>
   </si>
   <si>
     <t>[300002,1]</t>
@@ -1324,7 +1342,7 @@
         <v>1</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -1345,7 +1363,7 @@
         <v>1</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -1366,7 +1384,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -1387,7 +1405,7 @@
         <v>1</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -1408,7 +1426,7 @@
         <v>1</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -1429,7 +1447,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1440,7 +1458,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:3">

--- a/excel/sign.xlsx
+++ b/excel/sign.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12360"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -114,10 +114,10 @@
     <t>reward</t>
   </si>
   <si>
-    <t>string</t>
+    <t>int</t>
   </si>
   <si>
-    <t>int</t>
+    <t>string</t>
   </si>
   <si>
     <t>[200001,1000]</t>
@@ -328,12 +328,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1181,10 +1181,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>7</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:13">
